--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5959F7E3-E210-4F33-AC2E-ED022BCDD919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E54C7DE-053F-4D5A-A886-D56FB0F8BDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3765" yWindow="1395" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="840" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="266">
   <si>
     <t>SKU</t>
   </si>
@@ -439,39 +439,6 @@
     <t>£62.09</t>
   </si>
   <si>
-    <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
-  (Session info: chrome=150.0.7871.115)
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff731a8a865+152a5]
-	chromedriver!GetHandleVerifier [0x7ff731a8a8c0+15300]
-	chromedriver!(No symbol) [0x7ff7315e596d]
-	chromedriver!(No symbol) [0x7ff7315e2729]
-	chromedriver!(No symbol) [0x7ff7315d2ac1]
-	chromedriver!(No symbol) [0x7ff7315d492f]
-	chromedriver!(No symbol) [0x7ff7315d3063]
-	chromedriver!(No symbol) [0x7ff7315d282b]
-	chromedriver!(No symbol) [0x7ff7315d24e1]
-	chromedriver!(No symbol) [0x7ff7315d0197]
-	chromedriver!(No symbol) [0x7ff7315d0912]
-	chromedriver!(No symbol) [0x7ff7315e9c16]
-	chromedriver!(No symbol) [0x7ff73168eaf4]
-	chromedriver!(No symbol) [0x7ff731668e6a]
-	chromedriver!(No symbol) [0x7ff73168dcf4]
-	chromedriver!(No symbol) [0x7ff731632b3c]
-	chromedriver!(No symbol) [0x7ff731633a53]
-	chromedriver!GetHandleVerifier [0x7ff73206d3a1+5f7de1]
-	chromedriver!GetHandleVerifier [0x7ff732067a3b+5f247b]
-	chromedriver!GetHandleVerifier [0x7ff73208bca5+6166e5]
-	chromedriver!GetHandleVerifier [0x7ff731aa72ae+31cee]
-	chromedriver!GetHandleVerifier [0x7ff731aafe3c+3a87c]
-	chromedriver!GetHandleVerifier [0x7ff731a94404+1ee44]
-	chromedriver!GetHandleVerifier [0x7ff731a94594+1efd4]
-	chromedriver!GetHandleVerifier [0x7ff731a775c7+2007]
-	KERNEL32!BaseThreadInitThunk [0x7ff96b10e957+17]
-	ntdll!RtlUserThreadStart [0x7ff96d147c1c+2c]
-</t>
-  </si>
-  <si>
     <t>£23.17</t>
   </si>
   <si>
@@ -845,6 +812,12 @@
   </si>
   <si>
     <t>£711.4</t>
+  </si>
+  <si>
+    <t>£19.85</t>
+  </si>
+  <si>
+    <t>£54.21</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1261,7 @@
         <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G2" t="s">
         <v>90</v>
@@ -1300,31 +1273,31 @@
         <v>124</v>
       </c>
       <c r="J2" t="s">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="K2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L2" t="s">
         <v>89</v>
       </c>
       <c r="M2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P2" t="s">
         <v>81</v>
       </c>
       <c r="Q2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1344,7 +1317,7 @@
         <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G3" t="s">
         <v>91</v>
@@ -1356,19 +1329,19 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L3" t="s">
         <v>89</v>
       </c>
       <c r="M3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O3" t="s">
         <v>67</v>
@@ -1377,10 +1350,10 @@
         <v>81</v>
       </c>
       <c r="Q3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1400,7 +1373,7 @@
         <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G4" t="s">
         <v>92</v>
@@ -1412,19 +1385,19 @@
         <v>126</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L4" t="s">
         <v>89</v>
       </c>
       <c r="M4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O4" t="s">
         <v>68</v>
@@ -1433,10 +1406,10 @@
         <v>81</v>
       </c>
       <c r="Q4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1456,7 +1429,7 @@
         <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G5" t="s">
         <v>93</v>
@@ -1468,31 +1441,31 @@
         <v>127</v>
       </c>
       <c r="J5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L5" t="s">
         <v>89</v>
       </c>
       <c r="M5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P5" t="s">
         <v>81</v>
       </c>
       <c r="Q5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1512,7 +1485,7 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G6" t="s">
         <v>94</v>
@@ -1524,31 +1497,31 @@
         <v>128</v>
       </c>
       <c r="J6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L6" t="s">
         <v>89</v>
       </c>
       <c r="M6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P6" t="s">
         <v>81</v>
       </c>
       <c r="Q6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1568,7 +1541,7 @@
         <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G7" t="s">
         <v>95</v>
@@ -1580,16 +1553,16 @@
         <v>129</v>
       </c>
       <c r="J7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L7" t="s">
         <v>89</v>
       </c>
       <c r="M7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N7" t="s">
         <v>81</v>
@@ -1601,10 +1574,10 @@
         <v>81</v>
       </c>
       <c r="Q7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1624,7 +1597,7 @@
         <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G8" t="s">
         <v>95</v>
@@ -1636,31 +1609,31 @@
         <v>130</v>
       </c>
       <c r="J8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L8" t="s">
         <v>89</v>
       </c>
       <c r="M8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P8" t="s">
         <v>81</v>
       </c>
       <c r="Q8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1680,7 +1653,7 @@
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G9" t="s">
         <v>96</v>
@@ -1692,31 +1665,31 @@
         <v>131</v>
       </c>
       <c r="J9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L9" t="s">
         <v>89</v>
       </c>
       <c r="M9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P9" t="s">
         <v>81</v>
       </c>
       <c r="Q9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1736,7 +1709,7 @@
         <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G10" t="s">
         <v>97</v>
@@ -1748,10 +1721,10 @@
         <v>132</v>
       </c>
       <c r="J10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L10" t="s">
         <v>89</v>
@@ -1763,16 +1736,16 @@
         <v>81</v>
       </c>
       <c r="O10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P10" t="s">
         <v>81</v>
       </c>
       <c r="Q10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="R10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1792,7 +1765,7 @@
         <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G11" t="s">
         <v>98</v>
@@ -1804,31 +1777,31 @@
         <v>133</v>
       </c>
       <c r="J11" t="s">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="K11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L11" t="s">
         <v>89</v>
       </c>
       <c r="M11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P11" t="s">
         <v>81</v>
       </c>
       <c r="Q11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1848,7 +1821,7 @@
         <v>89</v>
       </c>
       <c r="F12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G12" t="s">
         <v>76</v>
@@ -1860,7 +1833,7 @@
         <v>134</v>
       </c>
       <c r="J12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K12" t="s">
         <v>89</v>
@@ -1869,7 +1842,7 @@
         <v>89</v>
       </c>
       <c r="M12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N12" t="s">
         <v>81</v>
@@ -1881,7 +1854,7 @@
         <v>81</v>
       </c>
       <c r="Q12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R12" t="s">
         <v>89</v>
@@ -1904,7 +1877,7 @@
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G13" t="s">
         <v>99</v>
@@ -1916,31 +1889,31 @@
         <v>135</v>
       </c>
       <c r="J13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s">
         <v>89</v>
       </c>
       <c r="M13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P13" t="s">
         <v>81</v>
       </c>
       <c r="Q13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1960,7 +1933,7 @@
         <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G14" t="s">
         <v>100</v>
@@ -1972,19 +1945,19 @@
         <v>136</v>
       </c>
       <c r="J14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s">
         <v>89</v>
       </c>
       <c r="M14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O14" t="s">
         <v>78</v>
@@ -1993,7 +1966,7 @@
         <v>81</v>
       </c>
       <c r="Q14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R14" t="s">
         <v>89</v>
@@ -2028,19 +2001,19 @@
         <v>137</v>
       </c>
       <c r="J15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s">
         <v>89</v>
       </c>
       <c r="M15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s">
         <v>79</v>
@@ -2049,7 +2022,7 @@
         <v>81</v>
       </c>
       <c r="Q15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R15" t="s">
         <v>89</v>
@@ -2072,7 +2045,7 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G16" t="s">
         <v>102</v>
@@ -2084,31 +2057,31 @@
         <v>138</v>
       </c>
       <c r="J16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s">
         <v>89</v>
       </c>
       <c r="M16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P16" t="s">
         <v>81</v>
       </c>
       <c r="Q16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2119,7 +2092,7 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D17" t="s">
         <v>81</v>
@@ -2196,7 +2169,7 @@
         <v>89</v>
       </c>
       <c r="J18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K18" t="s">
         <v>89</v>
@@ -2208,10 +2181,10 @@
         <v>89</v>
       </c>
       <c r="N18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s">
         <v>81</v>
@@ -2220,7 +2193,7 @@
         <v>89</v>
       </c>
       <c r="R18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2252,7 +2225,7 @@
         <v>89</v>
       </c>
       <c r="J19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K19" t="s">
         <v>89</v>
@@ -2264,10 +2237,10 @@
         <v>89</v>
       </c>
       <c r="N19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s">
         <v>81</v>
@@ -2276,7 +2249,7 @@
         <v>89</v>
       </c>
       <c r="R19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2308,7 +2281,7 @@
         <v>89</v>
       </c>
       <c r="J20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K20" t="s">
         <v>89</v>
@@ -2364,7 +2337,7 @@
         <v>89</v>
       </c>
       <c r="J21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K21" t="s">
         <v>89</v>
@@ -2420,7 +2393,7 @@
         <v>89</v>
       </c>
       <c r="J22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K22" t="s">
         <v>89</v>
@@ -2479,19 +2452,19 @@
         <v>89</v>
       </c>
       <c r="K23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L23" t="s">
         <v>89</v>
       </c>
       <c r="M23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P23" t="s">
         <v>89</v>
@@ -2500,7 +2473,7 @@
         <v>89</v>
       </c>
       <c r="R23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2535,7 +2508,7 @@
         <v>89</v>
       </c>
       <c r="K24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s">
         <v>89</v>
@@ -2544,10 +2517,10 @@
         <v>81</v>
       </c>
       <c r="N24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P24" t="s">
         <v>89</v>
@@ -2556,7 +2529,7 @@
         <v>89</v>
       </c>
       <c r="R24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2591,7 +2564,7 @@
         <v>89</v>
       </c>
       <c r="K25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L25" t="s">
         <v>89</v>
@@ -2600,10 +2573,10 @@
         <v>81</v>
       </c>
       <c r="N25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P25" t="s">
         <v>89</v>
@@ -2612,7 +2585,7 @@
         <v>89</v>
       </c>
       <c r="R25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
